--- a/docs/build/lakeshore-enterprise-context/source/05_treasury_kyriba/debt_fx_exposure.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/05_treasury_kyriba/debt_fx_exposure.xlsx
@@ -478,11 +478,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>93.2</v>
+        <v>495.2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6.64%</t>
+          <t>4.56%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -498,11 +498,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>249.9</v>
+        <v>336.9</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.35%</t>
+          <t>3.29%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -518,16 +518,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>452.9</v>
+        <v>151.3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5.63%</t>
+          <t>4.65%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Floating</t>
         </is>
       </c>
     </row>
@@ -538,11 +538,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>181</v>
+        <v>29</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>6.25%</t>
+          <t>5.27%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>595.6</v>
+        <v>297.4</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.62%</t>
+          <t>5.44%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Floating</t>
         </is>
       </c>
     </row>
@@ -578,16 +578,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>290.8</v>
+        <v>590.3</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4.05%</t>
+          <t>2.96%</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Floating</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
